--- a/src/assets/車籍資料表.xlsx
+++ b/src/assets/車籍資料表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>客戶代號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,15 +58,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>尿素卡號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>備註</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>開立統編</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡片狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡片刪除時間</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -409,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" customWidth="1"/>
@@ -417,14 +421,13 @@
     <col min="3" max="4" width="19.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="29.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="29.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="23.375" style="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -435,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -447,16 +450,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
